--- a/Assets/@Resources/Data/Excel/SkillData.xlsx
+++ b/Assets/@Resources/Data/Excel/SkillData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB23"/>
+  <dimension ref="A1:AE23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,21 @@
           <t>EffectDuration</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>StatTypes</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>StatBonuses</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>EffectVfxLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -699,11 +714,26 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>능력 고유 ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -718,12 +748,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>아이콘 라벨</t>
+          <t>아이콘</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>분류(Talent 등)</t>
+          <t>분류</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -738,7 +768,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>레벨당 버프 수치</t>
+          <t>레벨당 수치</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -753,32 +783,32 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>능력 이야기(로컬키)</t>
+          <t>이야기(로컬키)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>출처(Class/Minion/Equip/Npc/Unlimited)</t>
+          <t>출처</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>요구 미니몬 CreatureId</t>
+          <t>요구 미니몬ID</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>요구 장비 DataId</t>
+          <t>요구 장비ID</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>요구 재료 ItemId</t>
+          <t>요구 재료ID</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>요구 재료 개수</t>
+          <t>요구 재료수</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -788,12 +818,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>종류(Skill,Spell,Def,Util 콤마)</t>
+          <t>종류(콤마)</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>발동(None/Probability/Time)</t>
+          <t>발동</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -803,32 +833,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>확률 발동 %</t>
+          <t>확률%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>시간 발동 쿨(초)</t>
+          <t>쿨(초)</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>맥락(InBattle/OutOfBattle/Always)</t>
+          <t>맥락</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>조건 파라미터(LowHp%)</t>
+          <t>조건 파라미터</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>효과(Heal/BonusDamage/Buff)</t>
+          <t>효과</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Buff 대상 스탯</t>
+          <t>효과 스탯</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -838,7 +868,22 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Buff 지속(초,0=전투끝)</t>
+          <t>지속(초)</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>다중 스탯(콤마)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>다중 수치(콤마)</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>발동 VFX</t>
         </is>
       </c>
     </row>
@@ -856,7 +901,11 @@
           <t>Skill5009DescText</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AutoPotion Cooltime Skill Icon</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Talent</t>
@@ -867,7 +916,6 @@
           <t>Passive</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -877,7 +925,6 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>Npc</t>
@@ -890,19 +937,21 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>10003</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>연금공방</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
         <v>100</v>
       </c>
@@ -922,7 +971,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
@@ -944,7 +992,11 @@
           <t>Skill5001DescText</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Memory Expansion Icon</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Talent</t>
@@ -969,7 +1021,6 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>Unlimited</t>
@@ -987,14 +1038,11 @@
       <c r="P5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
         <v>100</v>
       </c>
@@ -1014,7 +1062,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
@@ -1036,7 +1083,11 @@
           <t>Skill5002DescText</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Skill5002</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -1083,14 +1134,11 @@
       <c r="P6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
         <v>100</v>
       </c>
@@ -1110,7 +1158,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
@@ -1132,7 +1179,11 @@
           <t>Skill5003DescText</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Skill5003</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -1184,13 +1235,11 @@
           <t>연금공방</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
         <v>100</v>
       </c>
@@ -1210,7 +1259,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
@@ -1232,7 +1280,11 @@
           <t>Skill5004DescText</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Skill5004</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -1279,14 +1331,11 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
         <v>100</v>
       </c>
@@ -1306,7 +1355,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
@@ -1328,7 +1376,11 @@
           <t>Skill7000DescText</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Skill7000</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Talent</t>
@@ -1353,7 +1405,6 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>Unlimited</t>
@@ -1371,14 +1422,11 @@
       <c r="P9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
         <v>100</v>
       </c>
@@ -1398,7 +1446,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
@@ -1420,7 +1467,11 @@
           <t>Skill7001DescText</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Skill7001</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Talent</t>
@@ -1445,7 +1496,6 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>Unlimited</t>
@@ -1463,14 +1513,11 @@
       <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
         <v>100</v>
       </c>
@@ -1490,7 +1537,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
@@ -1512,7 +1558,11 @@
           <t>Skill7002DescText</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Skill7002</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Talent</t>
@@ -1537,7 +1587,6 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>Unlimited</t>
@@ -1555,14 +1604,11 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
         <v>100</v>
       </c>
@@ -1582,7 +1628,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
@@ -1604,7 +1649,11 @@
           <t>Skill6001DescText</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pong's Adaptability Skill Icon</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -1651,14 +1700,11 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
         <v>100</v>
       </c>
@@ -1678,7 +1724,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
@@ -1700,7 +1745,11 @@
           <t>Skill6002DescText</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Skill6002</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -1725,7 +1774,6 @@
       <c r="J13" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>Minion</t>
@@ -1743,14 +1791,11 @@
       <c r="P13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
         <v>100</v>
       </c>
@@ -1770,7 +1815,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
@@ -1792,7 +1836,11 @@
           <t>Skill5005DescText</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Skill5005</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -1817,7 +1865,6 @@
       <c r="J14" t="n">
         <v>3</v>
       </c>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>Equip</t>
@@ -1835,8 +1882,6 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>Probability</t>
@@ -1866,7 +1911,6 @@
           <t>BonusDamage</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="n">
         <v>30</v>
       </c>
@@ -1888,7 +1932,11 @@
           <t>Skill5006DescText</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Skill5006</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -1913,7 +1961,6 @@
       <c r="J15" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>Npc</t>
@@ -1936,13 +1983,11 @@
           <t>연금공방</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
         <v>100</v>
       </c>
@@ -1962,7 +2007,6 @@
           <t>Heal</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
         <v>25</v>
       </c>
@@ -1984,7 +2028,11 @@
           <t>Skill5007DescText</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Skill5007</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -2009,7 +2057,6 @@
       <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>Class</t>
@@ -2027,8 +2074,6 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>Probability</t>
@@ -2084,7 +2129,11 @@
           <t>Skill5008DescText</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Skill5008</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -2109,7 +2158,6 @@
       <c r="J17" t="n">
         <v>3</v>
       </c>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>Unlimited</t>
@@ -2127,8 +2175,6 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>Probability</t>
@@ -2184,7 +2230,11 @@
           <t>Skill5012DescText</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Attact_Chance Icon</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -2231,14 +2281,11 @@
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
       <c r="U18" t="n">
         <v>100</v>
       </c>
@@ -2258,7 +2305,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
@@ -2280,7 +2326,11 @@
           <t>Skill5010DescText</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Skill5010</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -2327,14 +2377,11 @@
       <c r="P19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" t="n">
         <v>100</v>
       </c>
@@ -2354,7 +2401,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
@@ -2376,7 +2422,11 @@
           <t>Skill5011DescText</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Skill5011</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -2423,14 +2473,11 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" t="n">
         <v>100</v>
       </c>
@@ -2450,7 +2497,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
         <v>0</v>
       </c>
@@ -2472,7 +2518,11 @@
           <t>Skill5013DescText</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Skill5013</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -2519,7 +2569,6 @@
       <c r="P21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Skill,Def,Util</t>
@@ -2530,7 +2579,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" t="n">
         <v>100</v>
       </c>
@@ -2550,7 +2598,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="n">
         <v>0</v>
       </c>
@@ -2572,7 +2619,11 @@
           <t>Skill5014DescText</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Skill5014</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -2619,7 +2670,6 @@
       <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Skill,Spell</t>
@@ -2630,7 +2680,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
         <v>100</v>
       </c>
@@ -2650,7 +2699,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="n">
         <v>0</v>
       </c>
@@ -2672,7 +2720,11 @@
           <t>Skill5015DescText</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Skill5015</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>Memory</t>
@@ -2719,7 +2771,6 @@
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Skill,Spell,Def,Util</t>
@@ -2730,7 +2781,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
       <c r="U23" t="n">
         <v>100</v>
       </c>
@@ -2750,7 +2800,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="n">
         <v>0</v>
       </c>

--- a/Assets/@Resources/Data/Excel/SkillData.xlsx
+++ b/Assets/@Resources/Data/Excel/SkillData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE23"/>
+  <dimension ref="A1:AE68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2804,6 +2804,4136 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5100</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Skill5100NameText</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Skill5100DescText</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Skill5100</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>BattleStart</t>
+        </is>
+      </c>
+      <c r="U24" t="n">
+        <v>60</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>PhysicalAtk</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5101</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Skill5101NameText</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Skill5101DescText</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Skill5101</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>OnAttack</t>
+        </is>
+      </c>
+      <c r="U25" t="n">
+        <v>25</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>BonusDamage</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5102</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Skill5102NameText</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Skill5102DescText</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Skill5102</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>AfterAttack</t>
+        </is>
+      </c>
+      <c r="U26" t="n">
+        <v>30</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>CritRate</t>
+        </is>
+      </c>
+      <c r="AA26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>5103</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Skill5103NameText</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Skill5103DescText</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Skill5103</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
+        <v>20</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>5104</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Skill5104NameText</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Skill5104DescText</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Skill5104</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>OnCrit</t>
+        </is>
+      </c>
+      <c r="U28" t="n">
+        <v>45</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>AtkSpeed</t>
+        </is>
+      </c>
+      <c r="AA28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>5105</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Skill5105NameText</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Skill5105DescText</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Skill5105</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>ConsecutiveCrit</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
+        <v>100</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>BonusDamage</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>5106</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Skill5106NameText</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Skill5106DescText</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Skill5106</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>OnMiss</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
+        <v>70</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>5107</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Skill5107NameText</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Skill5107DescText</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Skill5107</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>EnemyEvade</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
+        <v>50</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>CritRate</t>
+        </is>
+      </c>
+      <c r="AA31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5108</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Skill5108NameText</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Skill5108DescText</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Skill5108</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>SelfEvade</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
+        <v>55</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>BonusDamage</t>
+        </is>
+      </c>
+      <c r="AA32" t="n">
+        <v>45</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>5109</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Skill5109NameText</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Skill5109DescText</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Skill5109</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>ConsecutiveEvade</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>100</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Evasion</t>
+        </is>
+      </c>
+      <c r="AA33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>5110</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Skill5110NameText</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Skill5110DescText</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Skill5110</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>OnDamaged</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>35</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>5111</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Skill5111NameText</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Skill5111DescText</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Skill5111</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>LowHp</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>100</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X35" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>PhysicalAtk</t>
+        </is>
+      </c>
+      <c r="AA35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5112</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Skill5112NameText</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Skill5112DescText</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Skill5112</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>EnemyLowHp</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>100</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>BonusDamage</t>
+        </is>
+      </c>
+      <c r="AA36" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>5113</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Skill5113NameText</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Skill5113DescText</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Skill5113</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>FatalDamage</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>40</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>5114</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Skill5114NameText</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Skill5114DescText</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Skill5114</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>OnHeal</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>50</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>5115</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Skill5115NameText</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Skill5115DescText</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Skill5115</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>100</v>
+      </c>
+      <c r="V39" t="n">
+        <v>12</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="AA39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>5116</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Skill5116NameText</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Skill5116DescText</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Skill5116</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>4</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>100</v>
+      </c>
+      <c r="V40" t="n">
+        <v>18</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>PhysicalAtk</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>5117</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Skill5117NameText</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Skill5117DescText</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Skill5117</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>4</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>100</v>
+      </c>
+      <c r="V41" t="n">
+        <v>16</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>CritRate</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5118</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Skill5118NameText</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Skill5118DescText</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Skill5118</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>100</v>
+      </c>
+      <c r="V42" t="n">
+        <v>15</v>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>AtkSpeed</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>5119</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Skill5119NameText</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Skill5119DescText</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Skill5119</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>100</v>
+      </c>
+      <c r="V43" t="n">
+        <v>20</v>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>35</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>5120</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Skill5120NameText</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Skill5120DescText</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Skill5120</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>100</v>
+      </c>
+      <c r="V44" t="n">
+        <v>14</v>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="AA44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>5121</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Skill5121NameText</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Skill5121DescText</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Skill5121</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>100</v>
+      </c>
+      <c r="V45" t="n">
+        <v>17</v>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Evasion</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>16</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5122</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Skill5122NameText</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Skill5122DescText</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Skill5122</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>100</v>
+      </c>
+      <c r="V46" t="n">
+        <v>22</v>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>BonusDamage</t>
+        </is>
+      </c>
+      <c r="AA46" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>5123</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Skill5123NameText</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Skill5123DescText</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Skill5123</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>PhysicalAtk</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>12</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>100</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>5124</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Skill5124NameText</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Skill5124DescText</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Skill5124</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>MagicAtk</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>10</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>100</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>5125</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Skill5125NameText</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Skill5125DescText</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Skill5125</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>120</v>
+      </c>
+      <c r="I49" t="n">
+        <v>5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>100</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>5126</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Skill5126NameText</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Skill5126DescText</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Skill5126</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>10</v>
+      </c>
+      <c r="I50" t="n">
+        <v>5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>100</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>5127</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Skill5127NameText</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Skill5127DescText</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Skill5127</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>CritRate</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>100</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>5128</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Skill5128NameText</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Skill5128DescText</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Skill5128</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>CritDamage</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>15</v>
+      </c>
+      <c r="I52" t="n">
+        <v>5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U52" t="n">
+        <v>100</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>5129</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Skill5129NameText</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Skill5129DescText</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Skill5129</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U53" t="n">
+        <v>100</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>5130</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Skill5130NameText</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Skill5130DescText</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Skill5130</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>AtkSpeed</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>6</v>
+      </c>
+      <c r="I54" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>3</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U54" t="n">
+        <v>100</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>5131</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Skill5131NameText</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Skill5131DescText</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Skill5131</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Evasion</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>4</v>
+      </c>
+      <c r="I55" t="n">
+        <v>5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U55" t="n">
+        <v>100</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5132</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Skill5132NameText</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Skill5132DescText</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Skill5132</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>RecoveryRate</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>10</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U56" t="n">
+        <v>100</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>5133</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Skill5133NameText</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Skill5133DescText</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Skill5133</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>MaxMemory</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>3</v>
+      </c>
+      <c r="I57" t="n">
+        <v>5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U57" t="n">
+        <v>100</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>5134</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Skill5134NameText</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Skill5134DescText</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Skill5134</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>PhysicalResist</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>5</v>
+      </c>
+      <c r="I58" t="n">
+        <v>4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U58" t="n">
+        <v>100</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>5135</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Skill5135NameText</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Skill5135DescText</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Skill5135</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ExpGain</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>8</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U59" t="n">
+        <v>100</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>5136</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Skill5136NameText</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Skill5136DescText</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Skill5136</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>GoldGain</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>10</v>
+      </c>
+      <c r="I60" t="n">
+        <v>5</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U60" t="n">
+        <v>100</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>5137</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Skill5137NameText</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Skill5137DescText</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Skill5137</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>DropRate</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>6</v>
+      </c>
+      <c r="I61" t="n">
+        <v>5</v>
+      </c>
+      <c r="J61" t="n">
+        <v>2</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U61" t="n">
+        <v>100</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>5138</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Skill5138NameText</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Skill5138DescText</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Skill5138</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CatchRate</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Minion</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U62" t="n">
+        <v>100</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>5139</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Skill5139NameText</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Skill5139DescText</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Skill5139</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>GuaranteedCatchReduce</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>3</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U63" t="n">
+        <v>100</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>5140</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Skill5140NameText</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Skill5140DescText</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Skill5140</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Convenience</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>InterestMax</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U64" t="n">
+        <v>100</v>
+      </c>
+      <c r="V64" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>5141</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Skill5141NameText</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Skill5141DescText</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Skill5141</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Convenience</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>PotionCooldown</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>8</v>
+      </c>
+      <c r="I65" t="n">
+        <v>4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>2</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Npc</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U65" t="n">
+        <v>100</v>
+      </c>
+      <c r="V65" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5142</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Skill5142NameText</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Skill5142DescText</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Skill5142</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Convenience</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>ComboKeep</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>10</v>
+      </c>
+      <c r="I66" t="n">
+        <v>4</v>
+      </c>
+      <c r="J66" t="n">
+        <v>2</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U66" t="n">
+        <v>100</v>
+      </c>
+      <c r="V66" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>5143</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Skill5143NameText</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Skill5143DescText</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Skill5143</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>EnhanceLuck</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I67" t="n">
+        <v>3</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Equip</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U67" t="n">
+        <v>100</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>5144</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Skill5144NameText</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Skill5144DescText</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Skill5144</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Convenience</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>MoveSpeed</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>6</v>
+      </c>
+      <c r="I68" t="n">
+        <v>3</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U68" t="n">
+        <v>100</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/SkillData.xlsx
+++ b/Assets/@Resources/Data/Excel/SkillData.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE68"/>
+  <dimension ref="A1:AE74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6935,6 +6935,462 @@
       </c>
       <c r="AB68" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>5200</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Skill5200NameText</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Skill5200DescText</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Skill5200</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U69" t="n">
+        <v>100</v>
+      </c>
+      <c r="V69" t="n">
+        <v>8</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>BonusDamage</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>FX_hit_10</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>5201</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Skill5201NameText</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Skill5201DescText</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Skill5201</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U70" t="n">
+        <v>100</v>
+      </c>
+      <c r="V70" t="n">
+        <v>20</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>HP Potion Ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>5202</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Skill5202NameText</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Skill5202DescText</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Skill5202</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>5</v>
+      </c>
+      <c r="J71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U71" t="n">
+        <v>100</v>
+      </c>
+      <c r="V71" t="n">
+        <v>30</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>PhysicalAtk</t>
+        </is>
+      </c>
+      <c r="AA71" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>Star_01_Anim_13_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>5203</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Skill5203NameText</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Skill5203DescText</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Skill5203</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U72" t="n">
+        <v>100</v>
+      </c>
+      <c r="V72" t="n">
+        <v>25</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>AtkSpeed</t>
+        </is>
+      </c>
+      <c r="AA72" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>Star_01_Anim_13_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>5204</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Skill5204NameText</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Skill5204DescText</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Skill5204</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>2</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U73" t="n">
+        <v>100</v>
+      </c>
+      <c r="V73" t="n">
+        <v>25</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="AA73" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>Star_01_Anim_13_a</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>5205</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Skill5205NameText</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Skill5205DescText</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Skill5205</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Combat</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Repeat</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>5</v>
+      </c>
+      <c r="J74" t="n">
+        <v>2</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Unlimited</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="U74" t="n">
+        <v>100</v>
+      </c>
+      <c r="V74" t="n">
+        <v>45</v>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>InBattle</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>BonusDamage</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>FX_hit_10</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Assets/@Resources/Data/Excel/SkillData.xlsx
+++ b/Assets/@Resources/Data/Excel/SkillData.xlsx
@@ -1661,7 +1661,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1700,16 +1700,21 @@
       <c r="P12" t="n">
         <v>0</v>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="U12" t="n">
         <v>100</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1721,14 +1726,24 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>HP Potion Ef</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1757,7 +1772,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Passive</t>
+          <t>Repeat</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1791,16 +1806,21 @@
       <c r="P13" t="n">
         <v>0</v>
       </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Skill</t>
+        </is>
+      </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="U13" t="n">
         <v>100</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1812,14 +1832,24 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Buff</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>AtkSpeed</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>8</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Star_01_Anim_13_a</t>
+        </is>
       </c>
     </row>
     <row r="14">

--- a/Assets/@Resources/Data/Excel/SkillData.xlsx
+++ b/Assets/@Resources/Data/Excel/SkillData.xlsx
@@ -1307,7 +1307,7 @@
         <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1360,6 +1360,16 @@
       </c>
       <c r="AB8" t="n">
         <v>0</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>MaxHp,Def</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>50,5</t>
+        </is>
       </c>
     </row>
     <row r="9">
